--- a/database/event/8914/event_8914_evp_summary.xlsx
+++ b/database/event/8914/event_8914_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5129</v>
+        <v>9.4381</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3954</v>
+        <v>1.547</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0177</v>
+        <v>3.3162</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5129</v>
+        <v>9.4381</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4113</v>
+        <v>3.3365</v>
       </c>
       <c r="G2" t="n">
         <v>6.1016</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4113</v>
+        <v>3.3365</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4113</v>
+        <v>3.3365</v>
       </c>
       <c r="J2" t="n">
         <v>6.1016</v>
@@ -529,7 +529,7 @@
         <v>201</v>
       </c>
       <c r="M2" t="n">
-        <v>8.5129</v>
+        <v>9.4381</v>
       </c>
       <c r="N2" t="n">
         <v>366</v>
@@ -538,81 +538,81 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>luchov</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1129</v>
+        <v>7.5016</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1659</v>
+        <v>1.2296</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4521</v>
+        <v>2.5447</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1129</v>
+        <v>7.5016</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1066</v>
+        <v>3.3007</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0063</v>
+        <v>4.2009</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1361</v>
+        <v>3.3007</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1747</v>
+        <v>3.3007</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0063</v>
+        <v>4.2009</v>
       </c>
       <c r="K3" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="L3" t="n">
-        <v>128</v>
+        <v>201</v>
       </c>
       <c r="M3" t="n">
-        <v>7.180999999999999</v>
+        <v>7.5016</v>
       </c>
       <c r="N3" t="n">
-        <v>323</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6001</v>
+        <v>7.0932</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0819</v>
+        <v>1.1627</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2449</v>
+        <v>2.382</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6001</v>
+        <v>7.0932</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3099</v>
+        <v>4.0869</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2902</v>
+        <v>3.0063</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4548</v>
+        <v>4.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4964</v>
+        <v>4.1747</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2902</v>
+        <v>3.0063</v>
       </c>
       <c r="K4" t="n">
         <v>195</v>
@@ -621,7 +621,7 @@
         <v>128</v>
       </c>
       <c r="M4" t="n">
-        <v>6.7866</v>
+        <v>7.180999999999999</v>
       </c>
       <c r="N4" t="n">
         <v>323</v>
@@ -630,47 +630,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>luchov</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9834</v>
+        <v>6.5789</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9808</v>
+        <v>1.0784</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9958</v>
+        <v>2.1771</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9834</v>
+        <v>6.5789</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7825</v>
+        <v>4.2887</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2009</v>
+        <v>2.2902</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7825</v>
+        <v>4.4216</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7825</v>
+        <v>4.4964</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2009</v>
+        <v>2.2902</v>
       </c>
       <c r="K5" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="L5" t="n">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="M5" t="n">
-        <v>5.9834</v>
+        <v>6.7866</v>
       </c>
       <c r="N5" t="n">
-        <v>366</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9685</v>
+        <v>6.455</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9782999999999999</v>
+        <v>1.0581</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9898</v>
+        <v>2.1278</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9685</v>
+        <v>6.455</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3277</v>
+        <v>0.8142</v>
       </c>
       <c r="G6" t="n">
         <v>5.6408</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3277</v>
+        <v>0.8142</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3277</v>
+        <v>0.8142</v>
       </c>
       <c r="J6" t="n">
         <v>5.6408</v>
@@ -713,7 +713,7 @@
         <v>201</v>
       </c>
       <c r="M6" t="n">
-        <v>5.9685</v>
+        <v>6.455</v>
       </c>
       <c r="N6" t="n">
         <v>366</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JBOEN</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6582</v>
+        <v>5.8371</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9275</v>
+        <v>0.9568</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8644</v>
+        <v>1.8816</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6582</v>
+        <v>5.8371</v>
       </c>
       <c r="F7" t="n">
-        <v>5.2459</v>
+        <v>3.8937</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4123</v>
+        <v>1.9434</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9226</v>
+        <v>3.8937</v>
       </c>
       <c r="I7" t="n">
-        <v>5.9778</v>
+        <v>3.8937</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4123</v>
+        <v>1.9434</v>
       </c>
       <c r="K7" t="n">
-        <v>195</v>
+        <v>115</v>
       </c>
       <c r="L7" t="n">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="M7" t="n">
-        <v>6.3901</v>
+        <v>5.8371</v>
       </c>
       <c r="N7" t="n">
-        <v>323</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>JBOEN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.1476</v>
+        <v>5.6301</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8438</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6582</v>
+        <v>1.7991</v>
       </c>
       <c r="E8" t="n">
-        <v>5.1476</v>
+        <v>5.6301</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2041</v>
+        <v>5.2178</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9434</v>
+        <v>0.4123</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2041</v>
+        <v>5.8784</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2041</v>
+        <v>5.9778</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9434</v>
+        <v>0.4123</v>
       </c>
       <c r="K8" t="n">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="L8" t="n">
-        <v>230</v>
+        <v>128</v>
       </c>
       <c r="M8" t="n">
-        <v>5.1475</v>
+        <v>6.3901</v>
       </c>
       <c r="N8" t="n">
-        <v>345</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bobeksde</t>
+          <t>Magnojez</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2783</v>
+        <v>4.8441</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7013</v>
+        <v>0.794</v>
       </c>
       <c r="D9" t="n">
-        <v>1.307</v>
+        <v>1.486</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2783</v>
+        <v>4.8441</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3914</v>
+        <v>4.3297</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8868</v>
+        <v>0.5144</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3914</v>
+        <v>4.4859</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3914</v>
+        <v>4.4859</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8868</v>
+        <v>0.5144</v>
       </c>
       <c r="K9" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L9" t="n">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2782</v>
+        <v>5.0003</v>
       </c>
       <c r="N9" t="n">
-        <v>242</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9756</v>
+        <v>4.6072</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.7552</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1847</v>
+        <v>1.3916</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9756</v>
+        <v>4.6072</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2853</v>
+        <v>3.9169</v>
       </c>
       <c r="G10" t="n">
         <v>0.6903</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2853</v>
+        <v>3.9169</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2853</v>
+        <v>3.9169</v>
       </c>
       <c r="J10" t="n">
         <v>0.6903</v>
@@ -897,7 +897,7 @@
         <v>230</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9756</v>
+        <v>4.6072</v>
       </c>
       <c r="N10" t="n">
         <v>345</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Magnojez</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.919</v>
+        <v>4.5313</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6424</v>
+        <v>0.7427</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1618</v>
+        <v>1.3614</v>
       </c>
       <c r="E11" t="n">
-        <v>3.919</v>
+        <v>4.5313</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4046</v>
+        <v>4.5313</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5144</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4046</v>
+        <v>4.802</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4046</v>
+        <v>4.802</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5144</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="L11" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.919</v>
+        <v>4.802</v>
       </c>
       <c r="N11" t="n">
-        <v>146</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>bobeksde</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7647</v>
+        <v>4.4062</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6171</v>
+        <v>0.7222</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0995</v>
+        <v>1.3115</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7647</v>
+        <v>4.4062</v>
       </c>
       <c r="F12" t="n">
-        <v>4.3708</v>
+        <v>1.5194</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6061</v>
+        <v>2.8868</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5504</v>
+        <v>1.5194</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5716</v>
+        <v>1.5194</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6061</v>
+        <v>2.8868</v>
       </c>
       <c r="K12" t="n">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="L12" t="n">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9655</v>
+        <v>4.4062</v>
       </c>
       <c r="N12" t="n">
-        <v>261</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5933</v>
+        <v>4.3456</v>
       </c>
       <c r="C13" t="n">
-        <v>0.589</v>
+        <v>0.7123</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0303</v>
+        <v>1.2874</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5933</v>
+        <v>4.3456</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1273</v>
+        <v>3.8796</v>
       </c>
       <c r="G13" t="n">
         <v>0.466</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1273</v>
+        <v>3.8796</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1419</v>
+        <v>3.9123</v>
       </c>
       <c r="J13" t="n">
         <v>0.466</v>
@@ -1035,7 +1035,7 @@
         <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6079</v>
+        <v>4.3783</v>
       </c>
       <c r="N13" t="n">
         <v>264</v>
@@ -1044,921 +1044,921 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>slaxejezzz</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.3254</v>
+        <v>3.8966</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5451</v>
+        <v>0.6387</v>
       </c>
       <c r="D14" t="n">
-        <v>0.922</v>
+        <v>1.1085</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3254</v>
+        <v>3.8966</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1999</v>
+        <v>4.5027</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1254</v>
+        <v>-0.6061</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1999</v>
+        <v>4.7572</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1999</v>
+        <v>4.7972</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1254</v>
+        <v>-0.6061</v>
       </c>
       <c r="K14" t="n">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="L14" t="n">
-        <v>230</v>
+        <v>74</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3253</v>
+        <v>4.1911</v>
       </c>
       <c r="N14" t="n">
-        <v>345</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.2054</v>
+        <v>3.7969</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5254</v>
+        <v>0.6224</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8735000000000001</v>
+        <v>1.0688</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2054</v>
+        <v>3.7969</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2054</v>
+        <v>3.3224</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.4745</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2054</v>
+        <v>3.3224</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2054</v>
+        <v>3.3224</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.4745</v>
       </c>
       <c r="K15" t="n">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2054</v>
+        <v>3.7969</v>
       </c>
       <c r="N15" t="n">
-        <v>179</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.081</v>
+        <v>3.5579</v>
       </c>
       <c r="C16" t="n">
-        <v>0.505</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8233</v>
+        <v>0.9736</v>
       </c>
       <c r="E16" t="n">
-        <v>3.081</v>
+        <v>3.5579</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6065</v>
+        <v>3.5579</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4745</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6065</v>
+        <v>3.5579</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6065</v>
+        <v>3.5579</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4745</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.081</v>
+        <v>3.5579</v>
       </c>
       <c r="N16" t="n">
-        <v>138</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>r3salt</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.0489</v>
+        <v>3.5579</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4998</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8103</v>
+        <v>0.9736</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0489</v>
+        <v>3.5579</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2452</v>
+        <v>3.4397</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1963</v>
+        <v>0.1182</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2452</v>
+        <v>3.4397</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2603</v>
+        <v>3.4397</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1963</v>
+        <v>0.1182</v>
       </c>
       <c r="K17" t="n">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M17" t="n">
-        <v>3.064</v>
+        <v>3.5579</v>
       </c>
       <c r="N17" t="n">
-        <v>264</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>slaxejezzz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6938</v>
+        <v>3.3254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4416</v>
+        <v>0.5451</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6669</v>
+        <v>0.8809</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6938</v>
+        <v>3.3254</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5756</v>
+        <v>1.1999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1182</v>
+        <v>2.1254</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5756</v>
+        <v>1.1999</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5756</v>
+        <v>1.1999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1182</v>
+        <v>2.1254</v>
       </c>
       <c r="K18" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="L18" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6938</v>
+        <v>3.3253</v>
       </c>
       <c r="N18" t="n">
-        <v>138</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>r3salt</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4715</v>
+        <v>3.0372</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4051</v>
+        <v>0.4978</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.7661</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4715</v>
+        <v>3.0372</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5512</v>
+        <v>3.2335</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.1963</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5512</v>
+        <v>3.2335</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5631</v>
+        <v>3.2607</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.1963</v>
       </c>
       <c r="K19" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="L19" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4834</v>
+        <v>3.0644</v>
       </c>
       <c r="N19" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.4197</v>
+        <v>3.0236</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3966</v>
+        <v>0.4956</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5561</v>
+        <v>0.7607</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4197</v>
+        <v>3.0236</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4197</v>
+        <v>3.7805</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.7569</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4197</v>
+        <v>3.7805</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4197</v>
+        <v>3.7805</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.7569</v>
       </c>
       <c r="K20" t="n">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4197</v>
+        <v>3.0236</v>
       </c>
       <c r="N20" t="n">
-        <v>173</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.408</v>
+        <v>2.8692</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3947</v>
+        <v>0.4703</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5514</v>
+        <v>0.6992</v>
       </c>
       <c r="E21" t="n">
-        <v>2.408</v>
+        <v>2.8692</v>
       </c>
       <c r="F21" t="n">
-        <v>2.408</v>
+        <v>2.2491</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.6201</v>
       </c>
       <c r="H21" t="n">
-        <v>2.408</v>
+        <v>2.2491</v>
       </c>
       <c r="I21" t="n">
-        <v>2.408</v>
+        <v>2.2491</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.6201</v>
       </c>
       <c r="K21" t="n">
-        <v>254</v>
+        <v>102</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M21" t="n">
-        <v>2.408</v>
+        <v>2.8692</v>
       </c>
       <c r="N21" t="n">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.3852</v>
+        <v>2.6429</v>
       </c>
       <c r="C22" t="n">
-        <v>0.391</v>
+        <v>0.4332</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5422</v>
+        <v>0.609</v>
       </c>
       <c r="E22" t="n">
-        <v>2.3852</v>
+        <v>2.6429</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3852</v>
+        <v>2.6429</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.3852</v>
+        <v>2.6429</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3852</v>
+        <v>2.6429</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>173</v>
+        <v>254</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.3852</v>
+        <v>2.6429</v>
       </c>
       <c r="N22" t="n">
-        <v>173</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.2767</v>
+        <v>2.6023</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3732</v>
+        <v>0.4266</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4984</v>
+        <v>0.5928</v>
       </c>
       <c r="E23" t="n">
-        <v>2.2767</v>
+        <v>2.6023</v>
       </c>
       <c r="F23" t="n">
-        <v>3.0336</v>
+        <v>2.6023</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7569</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.0336</v>
+        <v>2.6023</v>
       </c>
       <c r="I23" t="n">
-        <v>3.0336</v>
+        <v>2.6023</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7569</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L23" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.2767</v>
+        <v>2.6023</v>
       </c>
       <c r="N23" t="n">
-        <v>146</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>avid</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.2627</v>
+        <v>2.5127</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3709</v>
+        <v>0.4119</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4927</v>
+        <v>0.5571</v>
       </c>
       <c r="E24" t="n">
-        <v>2.2627</v>
+        <v>2.5127</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5449</v>
+        <v>2.5924</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2822</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5449</v>
+        <v>2.5924</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5449</v>
+        <v>2.6142</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2822</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="L24" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="M24" t="n">
-        <v>2.2627</v>
+        <v>2.5345</v>
       </c>
       <c r="N24" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.1225</v>
+        <v>2.431</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3479</v>
+        <v>0.3985</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4361</v>
+        <v>0.5246</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1225</v>
+        <v>2.431</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1225</v>
+        <v>2.431</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1225</v>
+        <v>2.431</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1225</v>
+        <v>2.431</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>254</v>
+        <v>173</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.1225</v>
+        <v>2.431</v>
       </c>
       <c r="N25" t="n">
-        <v>254</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Neityu</t>
+          <t>avid</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.8322</v>
+        <v>2.4066</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3003</v>
+        <v>0.3945</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3188</v>
+        <v>0.5149</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8322</v>
+        <v>2.4066</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4291</v>
+        <v>2.6888</v>
       </c>
       <c r="G26" t="n">
-        <v>2.2613</v>
+        <v>-0.2822</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4291</v>
+        <v>2.6888</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4331</v>
+        <v>2.6888</v>
       </c>
       <c r="J26" t="n">
-        <v>2.2613</v>
+        <v>-0.2822</v>
       </c>
       <c r="K26" t="n">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="L26" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="M26" t="n">
-        <v>1.8282</v>
+        <v>2.4066</v>
       </c>
       <c r="N26" t="n">
-        <v>323</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>eraa</t>
+          <t>Neityu</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.75</v>
+        <v>1.8354</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2869</v>
+        <v>0.3008</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2856</v>
+        <v>0.2873</v>
       </c>
       <c r="E27" t="n">
-        <v>1.75</v>
+        <v>1.8354</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3979</v>
+        <v>-0.4259</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3521</v>
+        <v>2.2613</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3979</v>
+        <v>-0.4259</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3979</v>
+        <v>-0.4331</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3521</v>
+        <v>2.2613</v>
       </c>
       <c r="K27" t="n">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L27" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="M27" t="n">
-        <v>1.75</v>
+        <v>1.8282</v>
       </c>
       <c r="N27" t="n">
-        <v>242</v>
+        <v>323</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>eraa</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6581</v>
+        <v>1.75</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2718</v>
+        <v>0.2869</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2485</v>
+        <v>0.2533</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6581</v>
+        <v>1.75</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6581</v>
+        <v>1.3979</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.3521</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6581</v>
+        <v>1.3979</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6581</v>
+        <v>1.3979</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.3521</v>
       </c>
       <c r="K28" t="n">
-        <v>174</v>
+        <v>102</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6581</v>
+        <v>1.75</v>
       </c>
       <c r="N28" t="n">
-        <v>174</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.6529</v>
+        <v>1.6586</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2709</v>
+        <v>0.2719</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2464</v>
+        <v>0.2169</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6529</v>
+        <v>1.6586</v>
       </c>
       <c r="F29" t="n">
-        <v>1.0328</v>
+        <v>1.6586</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6201</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.0328</v>
+        <v>1.6586</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0328</v>
+        <v>1.6586</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6201</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="L29" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.6529</v>
+        <v>1.6586</v>
       </c>
       <c r="N29" t="n">
-        <v>242</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3903</v>
+        <v>1.6426</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2279</v>
+        <v>0.2692</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1403</v>
+        <v>0.2105</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3903</v>
+        <v>1.6426</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3903</v>
+        <v>1.8705</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.2279</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3903</v>
+        <v>1.8705</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3903</v>
+        <v>1.8705</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.2279</v>
       </c>
       <c r="K30" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3903</v>
+        <v>1.6426</v>
       </c>
       <c r="N30" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3081</v>
+        <v>1.3903</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2144</v>
+        <v>0.2279</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1071</v>
+        <v>0.11</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3081</v>
+        <v>1.3903</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3081</v>
+        <v>1.3903</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3081</v>
+        <v>1.3903</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3081</v>
+        <v>1.3903</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3081</v>
+        <v>1.3903</v>
       </c>
       <c r="N31" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2687</v>
+        <v>1.3233</v>
       </c>
       <c r="C32" t="n">
-        <v>0.208</v>
+        <v>0.2169</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0912</v>
+        <v>0.0833</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2687</v>
+        <v>1.3233</v>
       </c>
       <c r="F32" t="n">
-        <v>1.2687</v>
+        <v>1.3233</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2687</v>
+        <v>1.3233</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2687</v>
+        <v>1.3233</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2687</v>
+        <v>1.3233</v>
       </c>
       <c r="N32" t="n">
-        <v>179</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9819</v>
+        <v>1.2687</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1609</v>
+        <v>0.208</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0247</v>
+        <v>0.0615</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9819</v>
+        <v>1.2687</v>
       </c>
       <c r="F33" t="n">
-        <v>1.2098</v>
+        <v>1.2687</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.2279</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2098</v>
+        <v>1.2687</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2098</v>
+        <v>1.2687</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2279</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="L33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9819</v>
+        <v>1.2687</v>
       </c>
       <c r="N33" t="n">
-        <v>138</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9464</v>
+        <v>1.2248</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1551</v>
+        <v>0.2008</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.039</v>
+        <v>0.0441</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9464</v>
+        <v>1.2248</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9464</v>
+        <v>1.2248</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9464</v>
+        <v>1.2248</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9464</v>
+        <v>1.2248</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9464</v>
+        <v>1.2248</v>
       </c>
       <c r="N34" t="n">
         <v>116</v>
@@ -2010,231 +2010,231 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MoDo</t>
+          <t>d1Ledez</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7295</v>
+        <v>1.0269</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1196</v>
+        <v>0.1683</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1267</v>
+        <v>-0.0348</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7295</v>
+        <v>1.0269</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7295</v>
+        <v>1.2973</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.2704</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7295</v>
+        <v>1.2973</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7295</v>
+        <v>1.2973</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.2704</v>
       </c>
       <c r="K35" t="n">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7295</v>
+        <v>1.0269</v>
       </c>
       <c r="N35" t="n">
-        <v>70</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mag1k3Y</t>
+          <t>upE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7038</v>
+        <v>0.9156</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1154</v>
+        <v>0.1501</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.137</v>
+        <v>-0.0791</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7038</v>
+        <v>0.9156</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7301</v>
+        <v>1.6227</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0263</v>
+        <v>-0.7071</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7301</v>
+        <v>1.6227</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7335</v>
+        <v>1.6227</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.0263</v>
+        <v>-0.7071</v>
       </c>
       <c r="K36" t="n">
-        <v>203</v>
+        <v>102</v>
       </c>
       <c r="L36" t="n">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.9156000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>264</v>
+        <v>242</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.699</v>
+        <v>0.8708</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1146</v>
+        <v>0.1427</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.139</v>
+        <v>-0.097</v>
       </c>
       <c r="E37" t="n">
-        <v>0.699</v>
+        <v>0.8708</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4985</v>
+        <v>3.6552</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7995</v>
+        <v>-2.7844</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4985</v>
+        <v>3.6552</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4985</v>
+        <v>3.6552</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7995</v>
+        <v>-2.7844</v>
       </c>
       <c r="K37" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="L37" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="M37" t="n">
-        <v>0.699</v>
+        <v>0.8707999999999996</v>
       </c>
       <c r="N37" t="n">
-        <v>138</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6807</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1116</v>
+        <v>0.1407</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1464</v>
+        <v>-0.1019</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6807</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7402</v>
+        <v>0.8339</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0595</v>
+        <v>0.0245</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7402</v>
+        <v>0.8339</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7437</v>
+        <v>0.8339</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.0595</v>
+        <v>0.0245</v>
       </c>
       <c r="K38" t="n">
-        <v>187</v>
+        <v>115</v>
       </c>
       <c r="L38" t="n">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6842</v>
+        <v>0.8583999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>261</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tex1y</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5409</v>
+        <v>0.8384</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0887</v>
+        <v>0.1374</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2029</v>
+        <v>-0.1099</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5409</v>
+        <v>0.8384</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3011</v>
+        <v>1.6379</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2398</v>
+        <v>-0.7995</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3011</v>
+        <v>1.6379</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3025</v>
+        <v>1.6379</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2398</v>
+        <v>-0.7995</v>
       </c>
       <c r="K39" t="n">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="L39" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5423</v>
+        <v>0.8383999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>264</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5331</v>
+        <v>0.7699</v>
       </c>
       <c r="C40" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.1262</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.206</v>
+        <v>-0.1372</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5331</v>
+        <v>0.7699</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5331</v>
+        <v>0.7699</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5331</v>
+        <v>0.7699</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5331</v>
+        <v>0.7699</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5331</v>
+        <v>0.7699</v>
       </c>
       <c r="N40" t="n">
         <v>102</v>
@@ -2286,829 +2286,829 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>upE</t>
+          <t>MoDo</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4291</v>
+        <v>0.7295</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0703</v>
+        <v>0.1196</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.248</v>
+        <v>-0.1533</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4291</v>
+        <v>0.7295</v>
       </c>
       <c r="F41" t="n">
-        <v>1.1362</v>
+        <v>0.7295</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1362</v>
+        <v>0.7295</v>
       </c>
       <c r="I41" t="n">
-        <v>1.1362</v>
+        <v>0.7295</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="L41" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4291000000000001</v>
+        <v>0.7295</v>
       </c>
       <c r="N41" t="n">
-        <v>242</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>mag1k3Y</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4158</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0682</v>
+        <v>0.1149</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2534</v>
+        <v>-0.1646</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4158</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4158</v>
+        <v>0.7274</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.0263</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4158</v>
+        <v>0.7274</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4158</v>
+        <v>0.7335</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.0263</v>
       </c>
       <c r="K42" t="n">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4158</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>173</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>venomzera</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2996</v>
+        <v>0.6867</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0491</v>
+        <v>0.1126</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3003</v>
+        <v>-0.1703</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2996</v>
+        <v>0.6867</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.3294</v>
+        <v>0.6867</v>
       </c>
       <c r="G43" t="n">
-        <v>0.629</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.3294</v>
+        <v>0.6867</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3309</v>
+        <v>0.6867</v>
       </c>
       <c r="J43" t="n">
-        <v>0.629</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="L43" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2981</v>
+        <v>0.6867</v>
       </c>
       <c r="N43" t="n">
-        <v>261</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2289</v>
+        <v>0.678</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0375</v>
+        <v>0.1111</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3289</v>
+        <v>-0.1738</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2289</v>
+        <v>0.678</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1416</v>
+        <v>0.7375</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0873</v>
+        <v>-0.0595</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1416</v>
+        <v>0.7375</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1416</v>
+        <v>0.7437</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0873</v>
+        <v>-0.0595</v>
       </c>
       <c r="K44" t="n">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="L44" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2289</v>
+        <v>0.6842</v>
       </c>
       <c r="N44" t="n">
-        <v>138</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.221</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0362</v>
+        <v>0.089</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3321</v>
+        <v>-0.2277</v>
       </c>
       <c r="E45" t="n">
-        <v>0.221</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1965</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0245</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1965</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1965</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0245</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>115</v>
+        <v>254</v>
       </c>
       <c r="L45" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.221</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>345</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>tex1y</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1994</v>
+        <v>0.5399</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0327</v>
+        <v>0.0885</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3408</v>
+        <v>-0.2288</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1994</v>
+        <v>0.5399</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.9377</v>
+        <v>0.3001</v>
       </c>
       <c r="G46" t="n">
-        <v>1.1371</v>
+        <v>0.2398</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.9377</v>
+        <v>0.3001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9377</v>
+        <v>0.3026</v>
       </c>
       <c r="J46" t="n">
-        <v>1.1371</v>
+        <v>0.2398</v>
       </c>
       <c r="K46" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="L46" t="n">
-        <v>201</v>
+        <v>61</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1994</v>
+        <v>0.5424</v>
       </c>
       <c r="N46" t="n">
-        <v>366</v>
+        <v>264</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>xKacpersky</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.5039</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0162</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3815</v>
+        <v>-0.2432</v>
       </c>
       <c r="E47" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.5039</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.5039</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.5039</v>
       </c>
       <c r="I47" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.5039</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.5039</v>
       </c>
       <c r="N47" t="n">
-        <v>174</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>d1Ledez</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.4158</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0158</v>
+        <v>0.0682</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3825</v>
+        <v>-0.2783</v>
       </c>
       <c r="E48" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.4158</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3666</v>
+        <v>0.4158</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.2704</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3666</v>
+        <v>0.4158</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3666</v>
+        <v>0.4158</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.2704</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L48" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.09620000000000001</v>
+        <v>0.4158</v>
       </c>
       <c r="N48" t="n">
-        <v>146</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>n0te</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0545</v>
+        <v>0.3009</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0089</v>
+        <v>0.0493</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4434</v>
+        <v>-0.324</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0545</v>
+        <v>0.3009</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.0545</v>
+        <v>-0.3281</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.629</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.0545</v>
+        <v>-0.3281</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0545</v>
+        <v>-0.3309</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.629</v>
       </c>
       <c r="K49" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0545</v>
+        <v>0.2981</v>
       </c>
       <c r="N49" t="n">
-        <v>174</v>
+        <v>261</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0887</v>
+        <v>0.2289</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0145</v>
+        <v>0.0375</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4572</v>
+        <v>-0.3527</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0887</v>
+        <v>0.2289</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0887</v>
+        <v>0.1416</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.0873</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0887</v>
+        <v>0.1416</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0887</v>
+        <v>0.1416</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.0873</v>
       </c>
       <c r="K50" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0887</v>
+        <v>0.2289</v>
       </c>
       <c r="N50" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1101</v>
+        <v>0.1994</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.018</v>
+        <v>0.0327</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4658</v>
+        <v>-0.3645</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1101</v>
+        <v>0.1994</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1101</v>
+        <v>-0.9377</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1.1371</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1101</v>
+        <v>-0.9377</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1101</v>
+        <v>-0.9377</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1.1371</v>
       </c>
       <c r="K51" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1101</v>
+        <v>0.1994</v>
       </c>
       <c r="N51" t="n">
-        <v>174</v>
+        <v>366</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1241</v>
+        <v>0.1696</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0203</v>
+        <v>0.0278</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4715</v>
+        <v>-0.3763</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1241</v>
+        <v>0.1696</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1241</v>
+        <v>0.1696</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1241</v>
+        <v>0.1696</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1241</v>
+        <v>0.1696</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1241</v>
+        <v>0.1696</v>
       </c>
       <c r="N52" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rainwaker</t>
+          <t>xKacpersky</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1634</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0268</v>
+        <v>0.0162</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4874</v>
+        <v>-0.4046</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1634</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1634</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1634</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1634</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1634</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>107</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>gr1ks</t>
+          <t>n0te</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1847</v>
+        <v>-0.0545</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0303</v>
+        <v>-0.0089</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.496</v>
+        <v>-0.4656</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1847</v>
+        <v>-0.0545</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2467</v>
+        <v>-0.0545</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.4314</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2467</v>
+        <v>-0.0545</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2478</v>
+        <v>-0.0545</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.4314</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="L54" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1836</v>
+        <v>-0.0545</v>
       </c>
       <c r="N54" t="n">
-        <v>261</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.196</v>
+        <v>-0.1101</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0321</v>
+        <v>-0.018</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.4878</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.196</v>
+        <v>-0.1101</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.196</v>
+        <v>-0.1101</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.196</v>
+        <v>-0.1101</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.196</v>
+        <v>-0.1101</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.196</v>
+        <v>-0.1101</v>
       </c>
       <c r="N55" t="n">
-        <v>254</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>venomzera</t>
+          <t>Rainwaker</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.244</v>
+        <v>-0.1634</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.04</v>
+        <v>-0.0268</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5199</v>
+        <v>-0.509</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.244</v>
+        <v>-0.1634</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.244</v>
+        <v>-0.1634</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.244</v>
+        <v>-0.1634</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.244</v>
+        <v>-0.1634</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.244</v>
+        <v>-0.1634</v>
       </c>
       <c r="N56" t="n">
-        <v>179</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>gr1ks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3229</v>
+        <v>-0.1857</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0529</v>
+        <v>-0.0304</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5518</v>
+        <v>-0.5179</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3229</v>
+        <v>-0.1857</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3229</v>
+        <v>0.2457</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-0.4314</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3229</v>
+        <v>0.2457</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3229</v>
+        <v>0.2478</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.4314</v>
       </c>
       <c r="K57" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3229</v>
+        <v>-0.1836</v>
       </c>
       <c r="N57" t="n">
-        <v>173</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4791</v>
+        <v>-0.3229</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0785</v>
+        <v>-0.0529</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6149</v>
+        <v>-0.5726</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4791</v>
+        <v>-0.3229</v>
       </c>
       <c r="F58" t="n">
-        <v>2.3053</v>
+        <v>-0.3229</v>
       </c>
       <c r="G58" t="n">
-        <v>-2.7844</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2.3053</v>
+        <v>-0.3229</v>
       </c>
       <c r="I58" t="n">
-        <v>2.3053</v>
+        <v>-0.3229</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.7844</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="L58" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4791000000000003</v>
+        <v>-0.3229</v>
       </c>
       <c r="N58" t="n">
-        <v>345</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59">
@@ -3124,7 +3124,7 @@
         <v>-0.0925</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6494</v>
+        <v>-0.6688</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5645</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.677</v>
+        <v>-0.6661</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.111</v>
+        <v>-0.1092</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6949</v>
+        <v>-0.7093</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.677</v>
+        <v>-0.6661</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.4603</v>
+        <v>-1.4494</v>
       </c>
       <c r="G60" t="n">
         <v>0.7833</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.4603</v>
+        <v>-1.4494</v>
       </c>
       <c r="I60" t="n">
         <v>-1.4739</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1239</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7268</v>
+        <v>-0.7451</v>
       </c>
       <c r="E61" t="n">
         <v>-0.756</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.8046</v>
+        <v>-0.7621</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1319</v>
+        <v>-0.1249</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7464</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8046</v>
+        <v>-0.7621</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.8046</v>
+        <v>-0.7621</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.8046</v>
+        <v>-0.7621</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.8046</v>
+        <v>-0.7621</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.8046</v>
+        <v>-0.7621</v>
       </c>
       <c r="N62" t="n">
         <v>102</v>
@@ -3308,7 +3308,7 @@
         <v>-0.1602</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8163</v>
+        <v>-0.8334</v>
       </c>
       <c r="E63" t="n">
         <v>-0.9776</v>
@@ -3354,7 +3354,7 @@
         <v>-0.1791</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8627</v>
+        <v>-0.8792</v>
       </c>
       <c r="E64" t="n">
         <v>-1.0925</v>
@@ -3400,7 +3400,7 @@
         <v>-0.1914</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.893</v>
+        <v>-0.9091</v>
       </c>
       <c r="E65" t="n">
         <v>-1.1676</v>
@@ -3446,7 +3446,7 @@
         <v>-0.1942</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8999</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="E66" t="n">
         <v>-1.1845</v>
@@ -3492,7 +3492,7 @@
         <v>-0.1962</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9049</v>
+        <v>-0.9208</v>
       </c>
       <c r="E67" t="n">
         <v>-1.1969</v>
@@ -3538,7 +3538,7 @@
         <v>-0.2258</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.978</v>
+        <v>-0.9928</v>
       </c>
       <c r="E68" t="n">
         <v>-1.3778</v>
@@ -3584,7 +3584,7 @@
         <v>-0.2526</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0439</v>
+        <v>-1.0578</v>
       </c>
       <c r="E69" t="n">
         <v>-1.541</v>
@@ -3630,7 +3630,7 @@
         <v>-0.2809</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1136</v>
+        <v>-1.1266</v>
       </c>
       <c r="E70" t="n">
         <v>-1.7135</v>
@@ -3676,7 +3676,7 @@
         <v>-0.291</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1385</v>
+        <v>-1.1512</v>
       </c>
       <c r="E71" t="n">
         <v>-1.7753</v>
@@ -3722,7 +3722,7 @@
         <v>-0.3029</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1678</v>
+        <v>-1.1801</v>
       </c>
       <c r="E72" t="n">
         <v>-1.8478</v>
@@ -3768,7 +3768,7 @@
         <v>-0.3115</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1892</v>
+        <v>-1.2011</v>
       </c>
       <c r="E73" t="n">
         <v>-1.9006</v>
@@ -3814,7 +3814,7 @@
         <v>-0.319</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2075</v>
+        <v>-1.2192</v>
       </c>
       <c r="E74" t="n">
         <v>-1.9461</v>
@@ -3860,7 +3860,7 @@
         <v>-0.3958</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3968</v>
+        <v>-1.4058</v>
       </c>
       <c r="E75" t="n">
         <v>-2.4145</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.9165</v>
+        <v>-2.6539</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.4781</v>
+        <v>-0.435</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.5996</v>
+        <v>-1.5012</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.9165</v>
+        <v>-2.6539</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1545</v>
+        <v>0.1081</v>
       </c>
       <c r="G76" t="n">
         <v>-2.762</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.1545</v>
+        <v>0.1081</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1545</v>
+        <v>0.1081</v>
       </c>
       <c r="J76" t="n">
         <v>-2.762</v>
@@ -3933,7 +3933,7 @@
         <v>201</v>
       </c>
       <c r="M76" t="n">
-        <v>-2.9165</v>
+        <v>-2.6539</v>
       </c>
       <c r="N76" t="n">
         <v>366</v>
@@ -3952,7 +3952,7 @@
         <v>-0.4904</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.6301</v>
+        <v>-1.6359</v>
       </c>
       <c r="E77" t="n">
         <v>-2.992</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-3.243</v>
+        <v>-3.2346</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5316</v>
+        <v>-0.5302</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.7315</v>
+        <v>-1.7326</v>
       </c>
       <c r="E78" t="n">
-        <v>-3.243</v>
+        <v>-3.2346</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.243</v>
+        <v>-2.2346</v>
       </c>
       <c r="G78" t="n">
         <v>-1</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.243</v>
+        <v>-2.2346</v>
       </c>
       <c r="I78" t="n">
         <v>-2.2534</v>
@@ -4044,7 +4044,7 @@
         <v>-0.5395</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.751</v>
+        <v>-1.7552</v>
       </c>
       <c r="E79" t="n">
         <v>-3.2913</v>
@@ -4090,7 +4090,7 @@
         <v>-0.5956</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8894</v>
+        <v>-1.8917</v>
       </c>
       <c r="E80" t="n">
         <v>-3.6339</v>
@@ -4136,7 +4136,7 @@
         <v>-0.5967</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8921</v>
+        <v>-1.8943</v>
       </c>
       <c r="E81" t="n">
         <v>-3.6406</v>

--- a/database/event/8914/event_8914_evp_summary.xlsx
+++ b/database/event/8914/event_8914_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.316700000000001</v>
+        <v>8.496700000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3632</v>
+        <v>1.3927</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1617</v>
+        <v>3.1815</v>
       </c>
       <c r="E2" t="n">
-        <v>8.316700000000001</v>
+        <v>8.496700000000001</v>
       </c>
       <c r="F2" t="n">
         <v>2.8725</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>luchov</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7385</v>
+        <v>6.961</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1045</v>
+        <v>1.141</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4433</v>
+        <v>2.4955</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7385</v>
+        <v>6.961</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7993</v>
+        <v>3.7225</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9392</v>
+        <v>2.9831</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4018</v>
+        <v>5.4224</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4018</v>
+        <v>5.7055</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9392</v>
+        <v>2.9831</v>
       </c>
       <c r="K3" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="L3" t="n">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>7.341</v>
+        <v>8.688599999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>366</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>luchov</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.7056</v>
+        <v>6.7726</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0991</v>
+        <v>1.1101</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4283</v>
+        <v>2.4114</v>
       </c>
       <c r="E4" t="n">
-        <v>6.7056</v>
+        <v>6.7726</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7225</v>
+        <v>2.7993</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9831</v>
+        <v>3.9392</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4224</v>
+        <v>3.4018</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7055</v>
+        <v>3.4018</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9831</v>
+        <v>3.9392</v>
       </c>
       <c r="K4" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="L4" t="n">
-        <v>128</v>
+        <v>201</v>
       </c>
       <c r="M4" t="n">
-        <v>8.688599999999999</v>
+        <v>7.341</v>
       </c>
       <c r="N4" t="n">
-        <v>323</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.306</v>
+        <v>6.4523</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0336</v>
+        <v>1.0576</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2464</v>
+        <v>2.2683</v>
       </c>
       <c r="E5" t="n">
-        <v>6.306</v>
+        <v>6.4523</v>
       </c>
       <c r="F5" t="n">
         <v>1.0955</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0648</v>
+        <v>6.1531</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9941</v>
+        <v>1.0086</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1366</v>
+        <v>2.1346</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0648</v>
+        <v>6.1531</v>
       </c>
       <c r="F6" t="n">
         <v>4.0275</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.2508</v>
+        <v>5.4256</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8607</v>
+        <v>0.8893</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7661</v>
+        <v>1.8097</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2508</v>
+        <v>5.4256</v>
       </c>
       <c r="F7" t="n">
         <v>4.5528</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>bobeksde</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.8736</v>
+        <v>5.0646</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.8302</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5944</v>
+        <v>1.6484</v>
       </c>
       <c r="E8" t="n">
-        <v>4.8736</v>
+        <v>5.0646</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1704</v>
+        <v>1.8889</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7032</v>
+        <v>2.9788</v>
       </c>
       <c r="H8" t="n">
-        <v>4.214</v>
+        <v>1.8889</v>
       </c>
       <c r="I8" t="n">
-        <v>4.214</v>
+        <v>1.8889</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7032</v>
+        <v>2.9788</v>
       </c>
       <c r="K8" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="L8" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="M8" t="n">
-        <v>5.9172</v>
+        <v>4.8677</v>
       </c>
       <c r="N8" t="n">
-        <v>345</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bobeksde</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.8677</v>
+        <v>5.0271</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5917</v>
+        <v>1.6317</v>
       </c>
       <c r="E9" t="n">
-        <v>4.8677</v>
+        <v>5.0271</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8889</v>
+        <v>3.1704</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9788</v>
+        <v>1.7032</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8889</v>
+        <v>4.214</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8889</v>
+        <v>4.214</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9788</v>
+        <v>1.7032</v>
       </c>
       <c r="K9" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="L9" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="M9" t="n">
-        <v>4.8677</v>
+        <v>5.9172</v>
       </c>
       <c r="N9" t="n">
-        <v>242</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3152</v>
+        <v>4.6681</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7073</v>
+        <v>0.7652</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3402</v>
+        <v>1.4713</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3152</v>
+        <v>4.6681</v>
       </c>
       <c r="F10" t="n">
         <v>3.7622</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0441</v>
+        <v>4.1353</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6629</v>
+        <v>0.6778</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2168</v>
+        <v>1.2333</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0441</v>
+        <v>4.1353</v>
       </c>
       <c r="F11" t="n">
         <v>2.9579</v>
@@ -952,311 +952,311 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>slaxejezzz</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.6388</v>
+        <v>3.884</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5965</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0323</v>
+        <v>1.1211</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6388</v>
+        <v>3.884</v>
       </c>
       <c r="F12" t="n">
-        <v>1.497</v>
+        <v>3.4761</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1418</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.497</v>
+        <v>4.8831</v>
       </c>
       <c r="I12" t="n">
-        <v>1.497</v>
+        <v>4.8831</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1418</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="L12" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6388</v>
+        <v>4.8831</v>
       </c>
       <c r="N12" t="n">
-        <v>345</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>Sdaim</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.4761</v>
+        <v>3.6085</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5698</v>
+        <v>0.5915</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.998</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4761</v>
+        <v>3.6085</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4761</v>
+        <v>3.012</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8831</v>
+        <v>3.8673</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8831</v>
+        <v>3.967</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="K13" t="n">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>4.8831</v>
+        <v>4.376</v>
       </c>
       <c r="N13" t="n">
-        <v>179</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Neityu</t>
+          <t>slaxejezzz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4232</v>
+        <v>3.5861</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5611</v>
+        <v>0.5878</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9341</v>
+        <v>0.988</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4232</v>
+        <v>3.5861</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1197</v>
+        <v>1.497</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3035</v>
+        <v>2.1418</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1197</v>
+        <v>1.497</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1781</v>
+        <v>1.497</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3035</v>
+        <v>2.1418</v>
       </c>
       <c r="K14" t="n">
-        <v>195</v>
+        <v>115</v>
       </c>
       <c r="L14" t="n">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4816</v>
+        <v>3.6388</v>
       </c>
       <c r="N14" t="n">
-        <v>323</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sdaim</t>
+          <t>Neityu</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.421</v>
+        <v>3.3098</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5608</v>
+        <v>0.5425</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9331</v>
+        <v>0.8646</v>
       </c>
       <c r="E15" t="n">
-        <v>3.421</v>
+        <v>3.3098</v>
       </c>
       <c r="F15" t="n">
-        <v>3.012</v>
+        <v>1.1197</v>
       </c>
       <c r="G15" t="n">
-        <v>0.409</v>
+        <v>2.3035</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8673</v>
+        <v>1.1197</v>
       </c>
       <c r="I15" t="n">
-        <v>3.967</v>
+        <v>1.1781</v>
       </c>
       <c r="J15" t="n">
-        <v>0.409</v>
+        <v>2.3035</v>
       </c>
       <c r="K15" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L15" t="n">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="M15" t="n">
-        <v>4.376</v>
+        <v>3.4816</v>
       </c>
       <c r="N15" t="n">
-        <v>264</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.1296</v>
+        <v>3.2858</v>
       </c>
       <c r="C16" t="n">
-        <v>0.513</v>
+        <v>0.5386</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8005</v>
+        <v>0.8539</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1296</v>
+        <v>3.2858</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4485</v>
+        <v>2.6656</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3189</v>
+        <v>0.3819</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8228</v>
+        <v>3.1092</v>
       </c>
       <c r="I16" t="n">
-        <v>4.9471</v>
+        <v>3.1092</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3189</v>
+        <v>0.3819</v>
       </c>
       <c r="K16" t="n">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="L16" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="M16" t="n">
-        <v>4.6282</v>
+        <v>3.4911</v>
       </c>
       <c r="N16" t="n">
-        <v>261</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.104</v>
+        <v>3.2414</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5088</v>
+        <v>0.5313</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7887999999999999</v>
+        <v>0.834</v>
       </c>
       <c r="E17" t="n">
-        <v>3.104</v>
+        <v>3.2414</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8038</v>
+        <v>3.4485</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3002</v>
+        <v>-0.3189</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4116</v>
+        <v>4.8228</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4116</v>
+        <v>4.9471</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3002</v>
+        <v>-0.3189</v>
       </c>
       <c r="K17" t="n">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="L17" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7118</v>
+        <v>4.6282</v>
       </c>
       <c r="N17" t="n">
-        <v>138</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.0475</v>
+        <v>3.0999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4995</v>
+        <v>0.5081</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7631</v>
+        <v>0.7708</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0475</v>
+        <v>3.0999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6656</v>
+        <v>2.8038</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3819</v>
+        <v>0.3002</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1092</v>
+        <v>3.4116</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1092</v>
+        <v>3.4116</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3819</v>
+        <v>0.3002</v>
       </c>
       <c r="K18" t="n">
         <v>78</v>
@@ -1265,7 +1265,7 @@
         <v>60</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4911</v>
+        <v>3.7118</v>
       </c>
       <c r="N18" t="n">
         <v>138</v>
@@ -1274,311 +1274,311 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.01</v>
+        <v>3.0448</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4934</v>
+        <v>0.4991</v>
       </c>
       <c r="D19" t="n">
-        <v>0.746</v>
+        <v>0.7462</v>
       </c>
       <c r="E19" t="n">
-        <v>3.01</v>
+        <v>3.0448</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2901</v>
+        <v>2.9631</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7199</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2901</v>
+        <v>3.7603</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2901</v>
+        <v>3.7603</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7199</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>102</v>
+        <v>254</v>
       </c>
       <c r="L19" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.01</v>
+        <v>3.7603</v>
       </c>
       <c r="N19" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9631</v>
+        <v>3.0088</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4857</v>
+        <v>0.4932</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7247</v>
+        <v>0.7301</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9631</v>
+        <v>3.0088</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9631</v>
+        <v>2.7243</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7603</v>
+        <v>3.2377</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7603</v>
+        <v>3.2377</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7603</v>
+        <v>3.2377</v>
       </c>
       <c r="N20" t="n">
-        <v>254</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>r3salt</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7968</v>
+        <v>2.9791</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4584</v>
+        <v>0.4883</v>
       </c>
       <c r="D21" t="n">
-        <v>0.649</v>
+        <v>0.7169</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7968</v>
+        <v>2.9791</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6609</v>
+        <v>2.2901</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1359</v>
+        <v>0.7199</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0989</v>
+        <v>2.2901</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1788</v>
+        <v>2.2901</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1359</v>
+        <v>0.7199</v>
       </c>
       <c r="K21" t="n">
-        <v>203</v>
+        <v>102</v>
       </c>
       <c r="L21" t="n">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3147</v>
+        <v>3.01</v>
       </c>
       <c r="N21" t="n">
-        <v>264</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>avid</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.7361</v>
+        <v>2.7692</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4485</v>
+        <v>0.4539</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6213</v>
+        <v>0.6231</v>
       </c>
       <c r="E22" t="n">
-        <v>2.7361</v>
+        <v>2.7692</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5097</v>
+        <v>2.6015</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2264</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.768</v>
+        <v>2.9689</v>
       </c>
       <c r="I22" t="n">
-        <v>2.768</v>
+        <v>2.9689</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2264</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>102</v>
+        <v>254</v>
       </c>
       <c r="L22" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9944</v>
+        <v>2.9689</v>
       </c>
       <c r="N22" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>r3salt</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.7243</v>
+        <v>2.7439</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4466</v>
+        <v>0.4498</v>
       </c>
       <c r="D23" t="n">
-        <v>0.616</v>
+        <v>0.6118</v>
       </c>
       <c r="E23" t="n">
-        <v>2.7243</v>
+        <v>2.7439</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7243</v>
+        <v>2.6609</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.1359</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2377</v>
+        <v>3.0989</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2377</v>
+        <v>3.1788</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.1359</v>
       </c>
       <c r="K23" t="n">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2377</v>
+        <v>3.3147</v>
       </c>
       <c r="N23" t="n">
-        <v>174</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>eraa</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.6015</v>
+        <v>2.6856</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4264</v>
+        <v>0.4402</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5601</v>
+        <v>0.5858</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6015</v>
+        <v>2.6856</v>
       </c>
       <c r="F24" t="n">
-        <v>2.6015</v>
+        <v>2.0506</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.5243</v>
       </c>
       <c r="H24" t="n">
-        <v>2.9689</v>
+        <v>2.0506</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9689</v>
+        <v>2.0506</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.5243</v>
       </c>
       <c r="K24" t="n">
-        <v>254</v>
+        <v>102</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9689</v>
+        <v>2.5749</v>
       </c>
       <c r="N24" t="n">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>eraa</t>
+          <t>avid</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.5749</v>
+        <v>2.6759</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4221</v>
+        <v>0.4386</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5814</v>
       </c>
       <c r="E25" t="n">
-        <v>2.5749</v>
+        <v>2.6759</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0506</v>
+        <v>2.5097</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5243</v>
+        <v>0.2264</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0506</v>
+        <v>2.768</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0506</v>
+        <v>2.768</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5243</v>
+        <v>0.2264</v>
       </c>
       <c r="K25" t="n">
         <v>102</v>
@@ -1587,7 +1587,7 @@
         <v>140</v>
       </c>
       <c r="M25" t="n">
-        <v>2.5749</v>
+        <v>2.9944</v>
       </c>
       <c r="N25" t="n">
         <v>242</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.5033</v>
+        <v>2.6281</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4103</v>
+        <v>0.4308</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5154</v>
+        <v>0.5601</v>
       </c>
       <c r="E26" t="n">
-        <v>2.5033</v>
+        <v>2.6281</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4619</v>
+        <v>2.4577</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0414</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6635</v>
+        <v>2.6541</v>
       </c>
       <c r="I26" t="n">
-        <v>2.7321</v>
+        <v>2.6541</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0414</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="L26" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.7735</v>
+        <v>2.6541</v>
       </c>
       <c r="N26" t="n">
-        <v>261</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.4577</v>
+        <v>2.6272</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4029</v>
+        <v>0.4306</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4946</v>
+        <v>0.5597</v>
       </c>
       <c r="E27" t="n">
-        <v>2.4577</v>
+        <v>2.6272</v>
       </c>
       <c r="F27" t="n">
-        <v>2.4577</v>
+        <v>2.4619</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.0414</v>
       </c>
       <c r="H27" t="n">
-        <v>2.6541</v>
+        <v>2.6635</v>
       </c>
       <c r="I27" t="n">
-        <v>2.6541</v>
+        <v>2.7321</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.0414</v>
       </c>
       <c r="K27" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M27" t="n">
-        <v>2.6541</v>
+        <v>2.7735</v>
       </c>
       <c r="N27" t="n">
-        <v>173</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28">
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.3604</v>
+        <v>2.5674</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3869</v>
+        <v>0.4208</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4503</v>
+        <v>0.533</v>
       </c>
       <c r="E28" t="n">
-        <v>2.3604</v>
+        <v>2.5674</v>
       </c>
       <c r="F28" t="n">
         <v>2.3604</v>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.2672</v>
+        <v>2.3891</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3716</v>
+        <v>0.3916</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4079</v>
+        <v>0.4533</v>
       </c>
       <c r="E29" t="n">
-        <v>2.2672</v>
+        <v>2.3891</v>
       </c>
       <c r="F29" t="n">
         <v>2.8546</v>
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.8666</v>
+        <v>1.8586</v>
       </c>
       <c r="C30" t="n">
-        <v>0.306</v>
+        <v>0.3047</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2255</v>
+        <v>0.2164</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8666</v>
+        <v>1.8586</v>
       </c>
       <c r="F30" t="n">
         <v>1.8666</v>
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.6104</v>
+        <v>1.5967</v>
       </c>
       <c r="C31" t="n">
-        <v>0.264</v>
+        <v>0.2617</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1089</v>
+        <v>0.0994</v>
       </c>
       <c r="E31" t="n">
-        <v>1.6104</v>
+        <v>1.5967</v>
       </c>
       <c r="F31" t="n">
         <v>1.706</v>
@@ -1872,185 +1872,185 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>venomzera</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.5821</v>
+        <v>1.5686</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2593</v>
+        <v>0.2571</v>
       </c>
       <c r="D32" t="n">
-        <v>0.096</v>
+        <v>0.0868</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5821</v>
+        <v>1.5686</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4037</v>
+        <v>1.5457</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1784</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4037</v>
+        <v>1.5457</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4399</v>
+        <v>1.5457</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1784</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="L32" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.6183</v>
+        <v>1.5457</v>
       </c>
       <c r="N32" t="n">
-        <v>261</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>venomzera</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.5457</v>
+        <v>1.529</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2534</v>
+        <v>0.2506</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0794</v>
+        <v>0.0692</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5457</v>
+        <v>1.529</v>
       </c>
       <c r="F33" t="n">
-        <v>1.5457</v>
+        <v>1.3719</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5457</v>
+        <v>1.3719</v>
       </c>
       <c r="I33" t="n">
-        <v>1.5457</v>
+        <v>1.3719</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>179</v>
+        <v>107</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.5457</v>
+        <v>1.3719</v>
       </c>
       <c r="N33" t="n">
-        <v>179</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.4437</v>
+        <v>1.4304</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2366</v>
+        <v>0.2345</v>
       </c>
       <c r="D34" t="n">
-        <v>0.033</v>
+        <v>0.0251</v>
       </c>
       <c r="E34" t="n">
-        <v>1.4437</v>
+        <v>1.4304</v>
       </c>
       <c r="F34" t="n">
-        <v>1.8878</v>
+        <v>1.4037</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4441</v>
+        <v>0.1784</v>
       </c>
       <c r="H34" t="n">
-        <v>1.8878</v>
+        <v>1.4037</v>
       </c>
       <c r="I34" t="n">
-        <v>1.8878</v>
+        <v>1.4399</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4441</v>
+        <v>0.1784</v>
       </c>
       <c r="K34" t="n">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="L34" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="M34" t="n">
-        <v>1.4437</v>
+        <v>1.6183</v>
       </c>
       <c r="N34" t="n">
-        <v>138</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>d1Ledez</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.3719</v>
+        <v>1.4025</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2249</v>
+        <v>0.2299</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0003</v>
+        <v>0.0126</v>
       </c>
       <c r="E35" t="n">
-        <v>1.3719</v>
+        <v>1.4025</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3719</v>
+        <v>1.5194</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.2767</v>
       </c>
       <c r="H35" t="n">
-        <v>1.3719</v>
+        <v>1.5194</v>
       </c>
       <c r="I35" t="n">
-        <v>1.3719</v>
+        <v>1.5194</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.2767</v>
       </c>
       <c r="K35" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M35" t="n">
-        <v>1.3719</v>
+        <v>1.2427</v>
       </c>
       <c r="N35" t="n">
-        <v>107</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.3286</v>
+        <v>1.3651</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2178</v>
+        <v>0.2238</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0194</v>
+        <v>-0.0041</v>
       </c>
       <c r="E36" t="n">
-        <v>1.3286</v>
+        <v>1.3651</v>
       </c>
       <c r="F36" t="n">
         <v>1.264</v>
@@ -2102,170 +2102,170 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.2954</v>
+        <v>1.3567</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2123</v>
+        <v>0.2224</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0345</v>
+        <v>-0.0078</v>
       </c>
       <c r="E37" t="n">
-        <v>1.2954</v>
+        <v>1.3567</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2954</v>
+        <v>1.8878</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.4441</v>
       </c>
       <c r="H37" t="n">
-        <v>1.2954</v>
+        <v>1.8878</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2954</v>
+        <v>1.8878</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.4441</v>
       </c>
       <c r="K37" t="n">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M37" t="n">
-        <v>1.2954</v>
+        <v>1.4437</v>
       </c>
       <c r="N37" t="n">
-        <v>116</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.2556</v>
+        <v>1.3317</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2058</v>
+        <v>0.2183</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0526</v>
+        <v>-0.019</v>
       </c>
       <c r="E38" t="n">
-        <v>1.2556</v>
+        <v>1.3317</v>
       </c>
       <c r="F38" t="n">
-        <v>1.2556</v>
+        <v>1.1821</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2556</v>
+        <v>1.1821</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2556</v>
+        <v>1.1821</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.2556</v>
+        <v>1.1821</v>
       </c>
       <c r="N38" t="n">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>d1Ledez</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.2427</v>
+        <v>1.2677</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2037</v>
+        <v>0.2078</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0585</v>
+        <v>-0.0476</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2427</v>
+        <v>1.2677</v>
       </c>
       <c r="F39" t="n">
-        <v>1.5194</v>
+        <v>1.2556</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.2767</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5194</v>
+        <v>1.2556</v>
       </c>
       <c r="I39" t="n">
-        <v>1.5194</v>
+        <v>1.2556</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.2767</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L39" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.2427</v>
+        <v>1.2556</v>
       </c>
       <c r="N39" t="n">
-        <v>146</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>z4KR</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.1821</v>
+        <v>1.2255</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1938</v>
+        <v>0.2009</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0861</v>
+        <v>-0.0664</v>
       </c>
       <c r="E40" t="n">
-        <v>1.1821</v>
+        <v>1.2255</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1821</v>
+        <v>1.2954</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1821</v>
+        <v>1.2954</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1821</v>
+        <v>1.2954</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.1821</v>
+        <v>1.2954</v>
       </c>
       <c r="N40" t="n">
         <v>116</v>
@@ -2286,369 +2286,369 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.1093</v>
+        <v>1.0659</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1818</v>
+        <v>0.1747</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1192</v>
+        <v>-0.1377</v>
       </c>
       <c r="E41" t="n">
-        <v>1.1093</v>
+        <v>1.0659</v>
       </c>
       <c r="F41" t="n">
-        <v>1.1093</v>
+        <v>0.9085</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1093</v>
+        <v>0.9085</v>
       </c>
       <c r="I41" t="n">
-        <v>1.1093</v>
+        <v>0.9085</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>254</v>
+        <v>102</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.1093</v>
+        <v>0.9085</v>
       </c>
       <c r="N41" t="n">
-        <v>254</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.0925</v>
+        <v>1.0646</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1791</v>
+        <v>0.1745</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1269</v>
+        <v>-0.1383</v>
       </c>
       <c r="E42" t="n">
-        <v>1.0925</v>
+        <v>1.0646</v>
       </c>
       <c r="F42" t="n">
-        <v>1.0503</v>
+        <v>1.1093</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0503</v>
+        <v>1.1093</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0503</v>
+        <v>1.1093</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>115</v>
+        <v>254</v>
       </c>
       <c r="L42" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.0925</v>
+        <v>1.1093</v>
       </c>
       <c r="N42" t="n">
-        <v>345</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.0704</v>
+        <v>1.0436</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1755</v>
+        <v>0.1711</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1369</v>
+        <v>-0.1477</v>
       </c>
       <c r="E43" t="n">
-        <v>1.0704</v>
+        <v>1.0436</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3017</v>
+        <v>1.0503</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7687</v>
+        <v>0.0422</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3017</v>
+        <v>1.0503</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3095</v>
+        <v>1.0503</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7687</v>
+        <v>0.0422</v>
       </c>
       <c r="K43" t="n">
-        <v>187</v>
+        <v>115</v>
       </c>
       <c r="L43" t="n">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="M43" t="n">
-        <v>1.0782</v>
+        <v>1.0925</v>
       </c>
       <c r="N43" t="n">
-        <v>261</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>upE</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.0582</v>
+        <v>0.9917</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1735</v>
+        <v>0.1626</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1425</v>
+        <v>-0.1708</v>
       </c>
       <c r="E44" t="n">
-        <v>1.0582</v>
+        <v>0.9917</v>
       </c>
       <c r="F44" t="n">
-        <v>1.5863</v>
+        <v>0.3017</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.5281</v>
+        <v>0.7687</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5863</v>
+        <v>0.3017</v>
       </c>
       <c r="I44" t="n">
-        <v>1.5863</v>
+        <v>0.3095</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.5281</v>
+        <v>0.7687</v>
       </c>
       <c r="K44" t="n">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="L44" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="M44" t="n">
-        <v>1.0582</v>
+        <v>1.0782</v>
       </c>
       <c r="N44" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>MoDo</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9085</v>
+        <v>0.9915</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1489</v>
+        <v>0.1625</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2106</v>
+        <v>-0.1709</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9085</v>
+        <v>0.9915</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9085</v>
+        <v>0.6794</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9085</v>
+        <v>0.6794</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9085</v>
+        <v>0.6794</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.9085</v>
+        <v>0.6794</v>
       </c>
       <c r="N45" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tex1y</t>
+          <t>upE</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7672</v>
+        <v>0.9389</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1258</v>
+        <v>0.1539</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.275</v>
+        <v>-0.1944</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7672</v>
+        <v>0.9389</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5178</v>
+        <v>1.5863</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2494</v>
+        <v>-0.5281</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5178</v>
+        <v>1.5863</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5311</v>
+        <v>1.5863</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2494</v>
+        <v>-0.5281</v>
       </c>
       <c r="K46" t="n">
-        <v>203</v>
+        <v>102</v>
       </c>
       <c r="L46" t="n">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7805</v>
+        <v>1.0582</v>
       </c>
       <c r="N46" t="n">
-        <v>264</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>tex1y</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.8807</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1176</v>
+        <v>0.1444</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2977</v>
+        <v>-0.2204</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.8807</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.5178</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.2494</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.5178</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.5311</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.2494</v>
       </c>
       <c r="K47" t="n">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7805</v>
       </c>
       <c r="N47" t="n">
-        <v>174</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MoDo</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6794</v>
+        <v>0.7117</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1114</v>
+        <v>0.1167</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3149</v>
+        <v>-0.2959</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6794</v>
+        <v>0.7117</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6794</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6794</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6794</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6794</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>70</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6653</v>
+        <v>0.5616</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1091</v>
+        <v>0.0921</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3213</v>
+        <v>-0.363</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6653</v>
+        <v>0.5616</v>
       </c>
       <c r="F49" t="n">
         <v>2.877</v>
@@ -2700,216 +2700,216 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.5316</v>
       </c>
       <c r="C50" t="n">
-        <v>0.106</v>
+        <v>0.0871</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3298</v>
+        <v>-0.3764</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.5316</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6467000000000001</v>
+        <v>-0.5508</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1.1365</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6467000000000001</v>
+        <v>-0.5508</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6467000000000001</v>
+        <v>-0.5508</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1.1365</v>
       </c>
       <c r="K50" t="n">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="M50" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.5857000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>116</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6256</v>
+        <v>0.5068</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1025</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3394</v>
+        <v>-0.3874</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6256</v>
+        <v>0.5068</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3615</v>
+        <v>-0.466</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2641</v>
+        <v>1.0294</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3615</v>
+        <v>-0.466</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3615</v>
+        <v>-0.4903</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2641</v>
+        <v>1.0294</v>
       </c>
       <c r="K51" t="n">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="L51" t="n">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6255999999999999</v>
+        <v>0.5391000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>138</v>
+        <v>323</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5857</v>
+        <v>0.467</v>
       </c>
       <c r="C52" t="n">
-        <v>0.096</v>
+        <v>0.0765</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3576</v>
+        <v>-0.4052</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5857</v>
+        <v>0.467</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.5508</v>
+        <v>0.4029</v>
       </c>
       <c r="G52" t="n">
-        <v>1.1365</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5508</v>
+        <v>0.4029</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.5508</v>
+        <v>0.4029</v>
       </c>
       <c r="J52" t="n">
-        <v>1.1365</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="L52" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5857000000000001</v>
+        <v>0.4029</v>
       </c>
       <c r="N52" t="n">
-        <v>366</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5634</v>
+        <v>0.4387</v>
       </c>
       <c r="C53" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3677</v>
+        <v>-0.4179</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5634</v>
+        <v>0.4387</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.466</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>1.0294</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.466</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.4903</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>1.0294</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="L53" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5391000000000001</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>323</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>xKacpersky</t>
+          <t>n0te</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4546</v>
+        <v>0.3825</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0745</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4173</v>
+        <v>-0.443</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4546</v>
+        <v>0.3825</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4546</v>
+        <v>0.387</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4546</v>
+        <v>0.387</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4546</v>
+        <v>0.387</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4546</v>
+        <v>0.387</v>
       </c>
       <c r="N54" t="n">
         <v>174</v>
@@ -2930,78 +2930,78 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4029</v>
+        <v>0.3669</v>
       </c>
       <c r="C55" t="n">
-        <v>0.066</v>
+        <v>0.0601</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4408</v>
+        <v>-0.4499</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4029</v>
+        <v>0.3669</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4029</v>
+        <v>0.3615</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>0.2641</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4029</v>
+        <v>0.3615</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4029</v>
+        <v>0.3615</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>0.2641</v>
       </c>
       <c r="K55" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4029</v>
+        <v>0.6255999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>n0te</t>
+          <t>xKacpersky</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.387</v>
+        <v>0.3658</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0634</v>
+        <v>0.06</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.448</v>
+        <v>-0.4504</v>
       </c>
       <c r="E56" t="n">
-        <v>0.387</v>
+        <v>0.3658</v>
       </c>
       <c r="F56" t="n">
-        <v>0.387</v>
+        <v>0.4546</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.387</v>
+        <v>0.4546</v>
       </c>
       <c r="I56" t="n">
-        <v>0.387</v>
+        <v>0.4546</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.387</v>
+        <v>0.4546</v>
       </c>
       <c r="N56" t="n">
         <v>174</v>
@@ -3026,16 +3026,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2689</v>
+        <v>0.3483</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0441</v>
+        <v>0.0571</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5018</v>
+        <v>-0.4582</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2689</v>
+        <v>0.3483</v>
       </c>
       <c r="F57" t="n">
         <v>0.5181</v>
@@ -3068,170 +3068,170 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>Rainwaker</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2397</v>
+        <v>0.1744</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0393</v>
+        <v>0.0286</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5151</v>
+        <v>-0.5359</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2397</v>
+        <v>0.1744</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2397</v>
+        <v>0.1092</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2397</v>
+        <v>0.1092</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2397</v>
+        <v>0.1092</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.2397</v>
+        <v>0.1092</v>
       </c>
       <c r="N58" t="n">
-        <v>173</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Rainwaker</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1092</v>
+        <v>0.1394</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0179</v>
+        <v>0.0228</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5745</v>
+        <v>-0.5516</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1092</v>
+        <v>0.1394</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1092</v>
+        <v>0.2397</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1092</v>
+        <v>0.2397</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1092</v>
+        <v>0.2397</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1092</v>
+        <v>0.2397</v>
       </c>
       <c r="N59" t="n">
-        <v>107</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2047</v>
+        <v>-0.1518</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0336</v>
+        <v>-0.0249</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7174</v>
+        <v>-0.6816</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2047</v>
+        <v>-0.1518</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2047</v>
+        <v>-0.4595</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2047</v>
+        <v>-0.4595</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2047</v>
+        <v>-0.4595</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2047</v>
+        <v>-0.4595</v>
       </c>
       <c r="N60" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AZUWU</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2455</v>
+        <v>-0.2061</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0402</v>
+        <v>-0.0338</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.736</v>
+        <v>-0.7059</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2455</v>
+        <v>-0.2061</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2455</v>
+        <v>-0.2047</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2455</v>
+        <v>-0.2047</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2455</v>
+        <v>-0.2047</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.2455</v>
+        <v>-0.2047</v>
       </c>
       <c r="N61" t="n">
         <v>107</v>
@@ -3252,139 +3252,139 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>AZUWU</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4595</v>
+        <v>-0.2095</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0343</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8334</v>
+        <v>-0.7074</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4595</v>
+        <v>-0.2095</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4595</v>
+        <v>-0.2455</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.4595</v>
+        <v>-0.2455</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.4595</v>
+        <v>-0.2455</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.4595</v>
+        <v>-0.2455</v>
       </c>
       <c r="N62" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>stressarN</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.3998</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0827</v>
+        <v>-0.0655</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8539</v>
+        <v>-0.7924</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.3998</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N63" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6892</v>
+        <v>-0.4912</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.113</v>
+        <v>-0.0805</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9379</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6892</v>
+        <v>-0.4912</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3108</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3108</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3108</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L64" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6892</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="N64" t="n">
-        <v>146</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65">
@@ -3394,16 +3394,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7068</v>
+        <v>-0.7779</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1159</v>
+        <v>-0.1275</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.946</v>
+        <v>-0.9613</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7068</v>
+        <v>-0.7779</v>
       </c>
       <c r="F65" t="n">
         <v>-0.7068</v>
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7621</v>
+        <v>-0.7985</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1249</v>
+        <v>-0.1309</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9711</v>
+        <v>-0.9705</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7621</v>
+        <v>-0.7985</v>
       </c>
       <c r="F66" t="n">
         <v>-0.7621</v>
@@ -3482,47 +3482,47 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>stressarN</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.8783</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1265</v>
+        <v>-0.144</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9755</v>
+        <v>-1.0061</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.8783</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7717000000000001</v>
+        <v>0.3108</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7717000000000001</v>
+        <v>0.3108</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7717000000000001</v>
+        <v>0.3108</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K67" t="n">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.6892</v>
       </c>
       <c r="N67" t="n">
-        <v>70</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68">
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7883</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.1292</v>
+        <v>-0.1594</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9831</v>
+        <v>-1.0481</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7883</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="F68" t="n">
         <v>-0.7883</v>
@@ -3578,16 +3578,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8067</v>
+        <v>-1.0678</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.1322</v>
+        <v>-0.175</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-1.0908</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8067</v>
+        <v>-1.0678</v>
       </c>
       <c r="F69" t="n">
         <v>-0.8067</v>
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0986</v>
+        <v>-1.3869</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.1801</v>
+        <v>-0.2273</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1243</v>
+        <v>-1.2333</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0986</v>
+        <v>-1.3869</v>
       </c>
       <c r="F70" t="n">
         <v>-1.0986</v>
@@ -3670,16 +3670,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.1612</v>
+        <v>-1.4257</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.1903</v>
+        <v>-0.2337</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1528</v>
+        <v>-1.2506</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.1612</v>
+        <v>-1.4257</v>
       </c>
       <c r="F71" t="n">
         <v>-1.1612</v>
@@ -3712,78 +3712,78 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>kisserek</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3754</v>
+        <v>-1.6473</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.2254</v>
+        <v>-0.27</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.2503</v>
+        <v>-1.3496</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3754</v>
+        <v>-1.6473</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.3754</v>
+        <v>-1.3924</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.3754</v>
+        <v>-1.3924</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.3754</v>
+        <v>-1.3924</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.3754</v>
+        <v>-1.3924</v>
       </c>
       <c r="N72" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kisserek</t>
+          <t>beastik</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.3924</v>
+        <v>-1.7662</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2282</v>
+        <v>-0.2895</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2581</v>
+        <v>-1.4027</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.3924</v>
+        <v>-1.7662</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.3924</v>
+        <v>-1.4367</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.3924</v>
+        <v>-1.4367</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.3924</v>
+        <v>-1.4367</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.3924</v>
+        <v>-1.4367</v>
       </c>
       <c r="N73" t="n">
         <v>70</v>
@@ -3804,47 +3804,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>beastik</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.4367</v>
+        <v>-1.8189</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.2355</v>
+        <v>-0.2981</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2782</v>
+        <v>-1.4263</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.4367</v>
+        <v>-1.8189</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.4367</v>
+        <v>-1.3754</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.4367</v>
+        <v>-1.3754</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.4367</v>
+        <v>-1.3754</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.4367</v>
+        <v>-1.3754</v>
       </c>
       <c r="N74" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75">
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.8678</v>
+        <v>-1.9456</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.3062</v>
+        <v>-0.3189</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.4745</v>
+        <v>-1.4829</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.8678</v>
+        <v>-1.9456</v>
       </c>
       <c r="F75" t="n">
         <v>-1.8678</v>
@@ -3900,16 +3900,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.891</v>
+        <v>-2.0482</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.31</v>
+        <v>-0.3357</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.485</v>
+        <v>-1.5287</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.891</v>
+        <v>-2.0482</v>
       </c>
       <c r="F76" t="n">
         <v>0.6138</v>
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.1639</v>
+        <v>-2.465</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.3547</v>
+        <v>-0.404</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.6093</v>
+        <v>-1.7149</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.1639</v>
+        <v>-2.465</v>
       </c>
       <c r="F77" t="n">
         <v>-2.1639</v>
@@ -3988,185 +3988,185 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SELLTER</t>
+          <t>dex</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.4426</v>
+        <v>-2.6951</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.4004</v>
+        <v>-0.4418</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.7361</v>
+        <v>-1.8177</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.4426</v>
+        <v>-2.6951</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.4426</v>
+        <v>-2.6544</v>
       </c>
       <c r="G78" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.4426</v>
+        <v>-2.6544</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.4798</v>
+        <v>-2.6544</v>
       </c>
       <c r="J78" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="L78" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.4798</v>
+        <v>-2.6544</v>
       </c>
       <c r="N78" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dex</t>
+          <t>SELLTER</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.6544</v>
+        <v>-2.836</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.4351</v>
+        <v>-0.4649</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.8325</v>
+        <v>-1.8806</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.6544</v>
+        <v>-2.836</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.6544</v>
+        <v>-1.4426</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.6544</v>
+        <v>-1.4426</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.6544</v>
+        <v>-1.4798</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K79" t="n">
-        <v>254</v>
+        <v>203</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.6544</v>
+        <v>-2.4798</v>
       </c>
       <c r="N79" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.7469</v>
+        <v>-3.2017</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.4503</v>
+        <v>-0.5248</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8746</v>
+        <v>-2.0439</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.7469</v>
+        <v>-3.2017</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.7469</v>
+        <v>-2.024</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>-0.8266</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.7469</v>
+        <v>-2.024</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.7469</v>
+        <v>-2.024</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>-0.8266</v>
       </c>
       <c r="K80" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.7469</v>
+        <v>-2.8506</v>
       </c>
       <c r="N80" t="n">
-        <v>102</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.8506</v>
+        <v>-3.2308</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.4673</v>
+        <v>-0.5296</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.9219</v>
+        <v>-2.0569</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.8506</v>
+        <v>-3.2308</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.024</v>
+        <v>-2.7469</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.8266</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.024</v>
+        <v>-2.7469</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.024</v>
+        <v>-2.7469</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.8266</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L81" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.8506</v>
+        <v>-2.7469</v>
       </c>
       <c r="N81" t="n">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
